--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,13 +362,13 @@
 </t>
   </si>
   <si>
-    <t>Lieu de naissance de la personne.</t>
+    <t>Lieu de naissance de la personne (Synonyme MOS : lieuNaissance).</t>
   </si>
   <si>
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Synonyme MOS : lieuNaissance</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>AD</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1135,7 +1135,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1341,7 +1341,7 @@
         <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1135,7 +1135,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1341,7 +1341,7 @@
         <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1135,7 +1135,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1341,7 +1341,7 @@
         <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1135,7 +1135,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1341,7 +1341,7 @@
         <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -355,7 +355,7 @@
     <t>valueAddress</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-1}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -355,7 +355,7 @@
     <t>valueAddress</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-3}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-birth-place.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
